--- a/ti-framework/data/TI_Data_Workbook_v0.1.xlsx
+++ b/ti-framework/data/TI_Data_Workbook_v0.1.xlsx
@@ -703,10 +703,14 @@
       <c r="J2" s="16" t="n">
         <v>3.933778670477284</v>
       </c>
-      <c r="K2" s="17" t="n"/>
+      <c r="K2" s="17" t="n">
+        <v>0.017473</v>
+      </c>
       <c r="L2" s="17" t="n"/>
       <c r="M2" s="17" t="n"/>
-      <c r="N2" s="17" t="n"/>
+      <c r="N2" s="17" t="n">
+        <v>0.110288</v>
+      </c>
       <c r="O2" s="17" t="n"/>
       <c r="P2" s="17" t="n"/>
       <c r="Q2" s="15" t="inlineStr">
@@ -716,7 +720,7 @@
       </c>
       <c r="R2" s="15" t="inlineStr">
         <is>
-          <t>UNFCCC NDC Registry; AU 2nd NDC 2025</t>
+          <t>UNFCCC NDC Registry; AU 2nd NDC 2025 · S1 sectoral: DCCEEW Australia's emissions projections 2025 baseline, transport 99(2025)→83(2035), electricity 148→46 MtCO2e; 2025→2035 CAGR (82% RE 2030 가정). 2035 NDC 추가 감축분 부문 미배분.</t>
         </is>
       </c>
     </row>
@@ -800,19 +804,23 @@
         <v>2.828092847637786</v>
       </c>
       <c r="K4" s="17" t="n"/>
-      <c r="L4" s="17" t="n"/>
+      <c r="L4" s="17" t="n">
+        <v>0.043451</v>
+      </c>
       <c r="M4" s="17" t="n"/>
       <c r="N4" s="17" t="n"/>
-      <c r="O4" s="17" t="n"/>
+      <c r="O4" s="17" t="n">
+        <v>0.072431</v>
+      </c>
       <c r="P4" s="17" t="n"/>
       <c r="Q4" s="15" t="inlineStr">
         <is>
-          <t>COMPUTED (pro-rata pending)</t>
+          <t>COMPUTED (sectoral S2)</t>
         </is>
       </c>
       <c r="R4" s="15" t="inlineStr">
         <is>
-          <t>UNFCCC; EU 2035 NDC Nov 2025</t>
+          <t>UNFCCC; EU 2035 NDC Nov 2025 · S2 sectoral: SWD(2024)63 Pt.3 Table 3 (Fit-for-55 경로) domestic transport 795.6(2023, Eurostat env_air_gge)→583(2030), power&amp;DH 573.8(CRF1A1A)→339 MtCO2e; 2023→2030 CAGR. 2035 부문치 공식 부재. PRIMES-CRF 정의차 ±0.5pp/yr.</t>
         </is>
       </c>
     </row>
@@ -854,19 +862,23 @@
         <v>4.079415217402316</v>
       </c>
       <c r="K5" s="17" t="n"/>
-      <c r="L5" s="17" t="n"/>
+      <c r="L5" s="17" t="n">
+        <v>0.036932</v>
+      </c>
       <c r="M5" s="17" t="n"/>
       <c r="N5" s="17" t="n"/>
-      <c r="O5" s="17" t="n"/>
+      <c r="O5" s="17" t="n">
+        <v>0.051362</v>
+      </c>
       <c r="P5" s="17" t="n"/>
       <c r="Q5" s="15" t="inlineStr">
         <is>
-          <t>COMPUTED (pro-rata pending)</t>
+          <t>COMPUTED (sectoral S2)</t>
         </is>
       </c>
       <c r="R5" s="15" t="inlineStr">
         <is>
-          <t>UNFCCC; JP 2035 NDC Feb 2025</t>
+          <t>UNFCCC; JP 2035 NDC Feb 2025 · S2 sectoral: 地球温暖化対策計画 (각의결정 2025-02-18) 運輸 190(FY2023)→146(FY2030), エネルギー転換(전기·열 배분후) 81.0→56 MtCO2; env.go.jp/content/000291669.pdf + 000310279.pdf. 2035 부문치 미공표 — FY2023→FY2030 CAGR 사용(2040 目安상 이후 더 가파름, 보수적).</t>
         </is>
       </c>
     </row>
@@ -908,19 +920,23 @@
         <v>5.388271494231722</v>
       </c>
       <c r="K6" s="17" t="n"/>
-      <c r="L6" s="17" t="n"/>
+      <c r="L6" s="17" t="n">
+        <v>0.060491</v>
+      </c>
       <c r="M6" s="17" t="n"/>
       <c r="N6" s="17" t="n"/>
-      <c r="O6" s="17" t="n"/>
+      <c r="O6" s="17" t="n">
+        <v>0.065024</v>
+      </c>
       <c r="P6" s="17" t="n"/>
       <c r="Q6" s="15" t="inlineStr">
         <is>
-          <t>COMPUTED (pro-rata pending)</t>
+          <t>COMPUTED (sectoral S2)</t>
         </is>
       </c>
       <c r="R6" s="15" t="inlineStr">
         <is>
-          <t>UNFCCC; KR 2035 NDC Dec 2025</t>
+          <t>UNFCCC; KR 2035 NDC Dec 2025 · S2 sectoral: 제1차 탄소중립·녹색성장 기본계획(2023.4) 연도별 경로 수송 88.7(2024)→61.0(2030), 전환 218.4→145.9 MtCO2eq; pcccr.go.kr. 2035 NDC(-53~61%)는 부문분해 미발표 — 2024→2030 CAGR 사용.</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1118,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="10">
       <c r="A12" s="18" t="inlineStr">
         <is>
@@ -1147,6 +1162,12 @@
       <c r="J13" s="9" t="n">
         <v>2.284003156575409</v>
       </c>
+      <c r="K13" s="9" t="n">
+        <v>0.019472</v>
+      </c>
+      <c r="N13" s="9" t="n">
+        <v>0.099132</v>
+      </c>
       <c r="Q13" s="9" t="inlineStr">
         <is>
           <t>COMPUTED (pro-rata pending)</t>
@@ -1154,7 +1175,7 @@
       </c>
       <c r="R13" s="9" t="inlineStr">
         <is>
-          <t>UNFCCC NDC Registry; CA 2035 NDC Feb 2025 (canada.ca); Grid: Ember 2024</t>
+          <t>UNFCCC NDC Registry; CA 2035 NDC Feb 2025 (canada.ca); Grid: Ember 2024 · S1 sectoral: ECCC 2025 ERP Progress Report, With-Measures projection transport 157(2023)→124(2035), electricity 49→14 MtCO2e; 2023→2035 CAGR. CER 최종안은 2035 넷제로 그리드 아님(2050).</t>
         </is>
       </c>
     </row>
@@ -1195,14 +1216,20 @@
       <c r="J14" s="9" t="n">
         <v>3.623244400122316</v>
       </c>
+      <c r="L14" s="9" t="n">
+        <v>0.08167199999999999</v>
+      </c>
+      <c r="O14" s="9" t="n">
+        <v>0.147623</v>
+      </c>
       <c r="Q14" s="9" t="inlineStr">
         <is>
-          <t>COMPUTED (pro-rata pending)</t>
+          <t>COMPUTED (sectoral S2)</t>
         </is>
       </c>
       <c r="R14" s="9" t="inlineStr">
         <is>
-          <t>UNFCCC NDC Registry; UK 2035 NDC Jan 2025 (gov.uk ICTU); Grid: Ember 2024</t>
+          <t>UNFCCC NDC Registry; UK 2035 NDC Jan 2025 (gov.uk ICTU); Grid: Ember 2024 · S2 sectoral: CCC 7th Carbon Budget Balanced Pathway (법정 자문, 정부 채택 아님) surface transport 102.8(2023)→36.98(2035), electricity supply 37.8→5.56 MtCO2e; full-dataset.xlsx, 2023→2035 CAGR.</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="9" min="1" max="1"/>
@@ -1295,22 +1322,42 @@
     <row r="2" ht="23.85" customHeight="1" s="10">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>Hyundai</t>
-        </is>
-      </c>
-      <c r="B2" s="17" t="n"/>
-      <c r="C2" s="17" t="n"/>
-      <c r="D2" s="17" t="n"/>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>Yaris HV (JP, WLTC)</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>HEV</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="E2" s="17" t="n"/>
-      <c r="F2" s="17" t="n"/>
+      <c r="F2" s="17" t="n">
+        <v>64.90000000000001</v>
+      </c>
       <c r="G2" s="17" t="n"/>
-      <c r="H2" s="17" t="n"/>
+      <c r="H2" s="17" t="n">
+        <v>1.25</v>
+      </c>
       <c r="I2" s="15" t="inlineStr">
         <is>
-          <t>EU type-approval / EPA / KR KEA / JP MLIT</t>
-        </is>
-      </c>
-      <c r="J2" s="17" t="n"/>
+          <t>MLIT 自動車燃費一覧 令和8年3月, WLTC 35.4–36.0 km/L ≈ 64–66 gCO2/km cert; mlit.go.jp/jidosha/content/001986923.xlsx</t>
+        </is>
+      </c>
+      <c r="J2" s="17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="K2" s="15" t="inlineStr">
         <is>
           <t>TO COLLECT</t>
@@ -1320,22 +1367,42 @@
     <row r="3" ht="23.85" customHeight="1" s="10">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Hyundai</t>
-        </is>
-      </c>
-      <c r="B3" s="17" t="n"/>
-      <c r="C3" s="17" t="n"/>
-      <c r="D3" s="17" t="n"/>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>Corolla (EU reg-weighted)</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>HEV</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="E3" s="17" t="n"/>
-      <c r="F3" s="17" t="n"/>
+      <c r="F3" s="17" t="n">
+        <v>111</v>
+      </c>
       <c r="G3" s="17" t="n"/>
-      <c r="H3" s="17" t="n"/>
+      <c r="H3" s="17" t="n">
+        <v>1.19</v>
+      </c>
       <c r="I3" s="15" t="inlineStr">
         <is>
-          <t>EU type-approval / EPA / KR KEA / JP MLIT</t>
-        </is>
-      </c>
-      <c r="J3" s="17" t="n"/>
+          <t>EEA CO2 monitoring 2022 provisional, n=86,017 registrations, avg WLTP; discodata.eea.europa.eu CO2Emission.latest.co2cars</t>
+        </is>
+      </c>
+      <c r="J3" s="17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="K3" s="15" t="inlineStr">
         <is>
           <t>TO COLLECT</t>
@@ -1345,22 +1412,42 @@
     <row r="4" ht="23.85" customHeight="1" s="10">
       <c r="A4" s="15" t="inlineStr">
         <is>
-          <t>Kia</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="n"/>
-      <c r="C4" s="17" t="n"/>
-      <c r="D4" s="17" t="n"/>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Yaris (EU reg-weighted)</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>HEV</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="E4" s="17" t="n"/>
-      <c r="F4" s="17" t="n"/>
+      <c r="F4" s="17" t="n">
+        <v>97</v>
+      </c>
       <c r="G4" s="17" t="n"/>
-      <c r="H4" s="17" t="n"/>
+      <c r="H4" s="17" t="n">
+        <v>1.19</v>
+      </c>
       <c r="I4" s="15" t="inlineStr">
         <is>
-          <t>EU type-approval / EPA / KR KEA / JP MLIT</t>
-        </is>
-      </c>
-      <c r="J4" s="17" t="n"/>
+          <t>EEA CO2 monitoring 2022P, n=126,263, avg WLTP</t>
+        </is>
+      </c>
+      <c r="J4" s="17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="K4" s="15" t="inlineStr">
         <is>
           <t>TO COLLECT</t>
@@ -1370,22 +1457,42 @@
     <row r="5" ht="23.85" customHeight="1" s="10">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Kia</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>RAV4 (EU reg-weighted)</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>HEV</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>C-SUV</t>
+        </is>
+      </c>
       <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="n"/>
+      <c r="F5" s="17" t="n">
+        <v>131</v>
+      </c>
       <c r="G5" s="17" t="n"/>
-      <c r="H5" s="17" t="n"/>
+      <c r="H5" s="17" t="n">
+        <v>1.19</v>
+      </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
-          <t>EU type-approval / EPA / KR KEA / JP MLIT</t>
-        </is>
-      </c>
-      <c r="J5" s="17" t="n"/>
+          <t>EEA CO2 monitoring 2022P, n=44,558, avg WLTP</t>
+        </is>
+      </c>
+      <c r="J5" s="17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="K5" s="15" t="inlineStr">
         <is>
           <t>TO COLLECT</t>
@@ -1398,19 +1505,41 @@
           <t>Toyota</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n"/>
-      <c r="C6" s="17" t="n"/>
-      <c r="D6" s="17" t="n"/>
-      <c r="E6" s="17" t="n"/>
-      <c r="F6" s="17" t="n"/>
-      <c r="G6" s="17" t="n"/>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>RAV4 PHEV (EU)</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>PHEV</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>C-SUV</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>0.75</v>
+      </c>
       <c r="H6" s="17" t="n"/>
       <c r="I6" s="15" t="inlineStr">
         <is>
-          <t>EU type-approval / EPA / KR KEA / JP MLIT</t>
-        </is>
-      </c>
-      <c r="J6" s="17" t="n"/>
+          <t>EEA 2022P n=9,540 avg WLTP 23 g/km, Z 165 Wh/km. Regulatory UF; real-world electric share ≈27% (COM(2024)122)</t>
+        </is>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="K6" s="15" t="inlineStr">
         <is>
           <t>TO COLLECT</t>
@@ -1423,19 +1552,39 @@
           <t>Toyota</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n"/>
-      <c r="C7" s="17" t="n"/>
-      <c r="D7" s="17" t="n"/>
-      <c r="E7" s="17" t="n"/>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>bZ4X (US label)</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>C-SUV</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0.192</v>
+      </c>
       <c r="F7" s="17" t="n"/>
       <c r="G7" s="17" t="n"/>
-      <c r="H7" s="17" t="n"/>
+      <c r="H7" s="17" t="n">
+        <v>1</v>
+      </c>
       <c r="I7" s="15" t="inlineStr">
         <is>
-          <t>EU type-approval / EPA / KR KEA / JP MLIT</t>
-        </is>
-      </c>
-      <c r="J7" s="17" t="n"/>
+          <t>EPA fueleconomy.gov MY2024 combE avg Toyota EV trims (label, real-world adjusted)</t>
+        </is>
+      </c>
+      <c r="J7" s="17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="K7" s="15" t="inlineStr">
         <is>
           <t>TO COLLECT</t>
@@ -1445,22 +1594,42 @@
     <row r="8" ht="23.85" customHeight="1" s="10">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>Honda</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="n"/>
-      <c r="C8" s="17" t="n"/>
-      <c r="D8" s="17" t="n"/>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>US hybrid trims (unweighted)</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>HEV</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
       <c r="E8" s="17" t="n"/>
-      <c r="F8" s="17" t="n"/>
+      <c r="F8" s="17" t="n">
+        <v>175</v>
+      </c>
       <c r="G8" s="17" t="n"/>
-      <c r="H8" s="17" t="n"/>
+      <c r="H8" s="17" t="n">
+        <v>1</v>
+      </c>
       <c r="I8" s="15" t="inlineStr">
         <is>
-          <t>EU type-approval / EPA / KR KEA / JP MLIT</t>
-        </is>
-      </c>
-      <c r="J8" s="17" t="n"/>
+          <t>EPA fueleconomy.gov MY2024, 36 hybrid trims, label CO2 avg (incl. Tundra/Sienna large HEVs)</t>
+        </is>
+      </c>
+      <c r="J8" s="17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="K8" s="15" t="inlineStr">
         <is>
           <t>TO COLLECT</t>
@@ -1470,22 +1639,42 @@
     <row r="9" ht="23.85" customHeight="1" s="10">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>Nissan</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="17" t="n"/>
-      <c r="D9" s="17" t="n"/>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>US ICE trims (unweighted)</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
       <c r="E9" s="17" t="n"/>
-      <c r="F9" s="17" t="n"/>
+      <c r="F9" s="17" t="n">
+        <v>231</v>
+      </c>
       <c r="G9" s="17" t="n"/>
-      <c r="H9" s="17" t="n"/>
+      <c r="H9" s="17" t="n">
+        <v>1</v>
+      </c>
       <c r="I9" s="15" t="inlineStr">
         <is>
-          <t>EU type-approval / EPA / KR KEA / JP MLIT</t>
-        </is>
-      </c>
-      <c r="J9" s="17" t="n"/>
+          <t>EPA fueleconomy.gov MY2024, 51 ICE trims, label CO2 avg</t>
+        </is>
+      </c>
+      <c r="J9" s="17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="K9" s="15" t="inlineStr">
         <is>
           <t>TO COLLECT</t>
@@ -1493,16 +1682,44 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="10">
-      <c r="A10" s="17" t="n"/>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="17" t="n"/>
-      <c r="D10" s="17" t="n"/>
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Hyundai</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Tucson (EU reg-weighted)</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>C-SUV</t>
+        </is>
+      </c>
       <c r="E10" s="17" t="n"/>
-      <c r="F10" s="17" t="n"/>
+      <c r="F10" s="17" t="n">
+        <v>142</v>
+      </c>
       <c r="G10" s="17" t="n"/>
-      <c r="H10" s="17" t="n"/>
-      <c r="I10" s="15" t="n"/>
-      <c r="J10" s="17" t="n"/>
+      <c r="H10" s="17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>EEA CO2 monitoring 2022P, n=43,475, avg WLTP</t>
+        </is>
+      </c>
+      <c r="J10" s="17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="K10" s="15" t="inlineStr">
         <is>
           <t>TO COLLECT</t>
@@ -1510,16 +1727,44 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="10">
-      <c r="A11" s="17" t="n"/>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="17" t="n"/>
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Hyundai</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>i20 (EU reg-weighted)</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="E11" s="17" t="n"/>
-      <c r="F11" s="17" t="n"/>
+      <c r="F11" s="17" t="n">
+        <v>119</v>
+      </c>
       <c r="G11" s="17" t="n"/>
-      <c r="H11" s="17" t="n"/>
-      <c r="I11" s="15" t="n"/>
-      <c r="J11" s="17" t="n"/>
+      <c r="H11" s="17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>EEA CO2 monitoring 2022P, n=36,909, avg WLTP</t>
+        </is>
+      </c>
+      <c r="J11" s="17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="K11" s="15" t="inlineStr">
         <is>
           <t>TO COLLECT</t>
@@ -1527,16 +1772,46 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="10">
-      <c r="A12" s="17" t="n"/>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="17" t="n"/>
-      <c r="D12" s="17" t="n"/>
-      <c r="E12" s="17" t="n"/>
-      <c r="F12" s="17" t="n"/>
-      <c r="G12" s="17" t="n"/>
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Hyundai</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Tucson PHEV (EU)</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>PHEV</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>C-SUV</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>0.7</v>
+      </c>
       <c r="H12" s="17" t="n"/>
-      <c r="I12" s="15" t="n"/>
-      <c r="J12" s="17" t="n"/>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>EEA 2022P n=12,214 avg WLTP 42 g/km, Z 177 Wh/km. Regulatory UF; real-world share ≈27% (COM(2024)122)</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="K12" s="15" t="inlineStr">
         <is>
           <t>TO COLLECT</t>
@@ -1544,16 +1819,44 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="10">
-      <c r="A13" s="17" t="n"/>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="17" t="n"/>
-      <c r="D13" s="17" t="n"/>
-      <c r="E13" s="17" t="n"/>
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Hyundai</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Ioniq 5 (EU reg-weighted)</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>C-SUV</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0.174</v>
+      </c>
       <c r="F13" s="17" t="n"/>
       <c r="G13" s="17" t="n"/>
-      <c r="H13" s="17" t="n"/>
-      <c r="I13" s="15" t="n"/>
-      <c r="J13" s="17" t="n"/>
+      <c r="H13" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>EEA CO2 monitoring 2022P, n=29,186, avg Z 174 Wh/km (cert)</t>
+        </is>
+      </c>
+      <c r="J13" s="17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="K13" s="15" t="inlineStr">
         <is>
           <t>TO COLLECT</t>
@@ -1561,16 +1864,44 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="10">
-      <c r="A14" s="17" t="n"/>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="17" t="n"/>
-      <c r="D14" s="17" t="n"/>
-      <c r="E14" s="17" t="n"/>
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Hyundai</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Kona EV (EU reg-weighted)</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>B-SUV</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>0.145</v>
+      </c>
       <c r="F14" s="17" t="n"/>
       <c r="G14" s="17" t="n"/>
-      <c r="H14" s="17" t="n"/>
-      <c r="I14" s="15" t="n"/>
-      <c r="J14" s="17" t="n"/>
+      <c r="H14" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>EEA CO2 monitoring 2022P, n=13,668+17,445, avg Z 145 Wh/km</t>
+        </is>
+      </c>
+      <c r="J14" s="17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="K14" s="15" t="inlineStr">
         <is>
           <t>TO COLLECT</t>
@@ -1578,19 +1909,161 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="10">
-      <c r="A15" s="17" t="n"/>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="17" t="n"/>
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Hyundai</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Ioniq 5 (KR label)</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>C-SUV</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>0.204</v>
+      </c>
       <c r="F15" s="17" t="n"/>
       <c r="G15" s="17" t="n"/>
-      <c r="H15" s="17" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="17" t="n"/>
+      <c r="H15" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>KEA 자동차 표시연비 2026-04, 복합 4.8–5.1 km/kWh (label incl. charging loss); data.go.kr/data/15083023</t>
+        </is>
+      </c>
+      <c r="J15" s="17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="K15" s="15" t="inlineStr">
         <is>
           <t>TO COLLECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Hyundai</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Grandeur HEV (KR label)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HEV</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>154</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>KEA 표시연비, 복합 14.9–15.9 km/L → ≈150–157 gCO2/km at 2,347 gCO2/L gasoline</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Hyundai</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>US hybrid trims (unweighted)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HEV</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>135</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>EPA fueleconomy.gov MY2024, 7 hybrid trims, label CO2 avg</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Hyundai</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>US ICE trims (unweighted)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>211</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>EPA fueleconomy.gov MY2024, 27 ICE trims, label CO2 avg</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
